--- a/Rapid Cortex Internal Docs/Archive/Rapid cortex pricing.xlsx
+++ b/Rapid Cortex Internal Docs/Archive/Rapid cortex pricing.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Mac Mini/Coding Projects/Hibernation/WebApp/Rapid Cortex/Rapid Cortex Pricing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Mac Mini/Coding Projects/Hibernation/WebApp/NexCort iQ/NexCort iQ Pricing/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{4F02D389-909E-E149-9299-9FDB4D6873A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -13,9 +13,9 @@
     <workbookView xWindow="-29480" yWindow="1860" windowWidth="28040" windowHeight="17440" xr2:uid="{976490BB-F09C-7349-B92C-4696FF776F89}"/>
   </bookViews>
   <sheets>
-    <sheet name="Rapid Cortex Essential" sheetId="1" r:id="rId1"/>
-    <sheet name="Rapid Cortex Professional" sheetId="2" r:id="rId2"/>
-    <sheet name="Rapid Cortex Command" sheetId="3" r:id="rId3"/>
+    <sheet name="NexCort iQ Essential" sheetId="1" r:id="rId1"/>
+    <sheet name="NexCort iQ Professional" sheetId="2" r:id="rId2"/>
+    <sheet name="NexCort iQ Command" sheetId="3" r:id="rId3"/>
     <sheet name="Enterprise_Statewide" sheetId="4" r:id="rId4"/>
     <sheet name="CAD Integration" sheetId="5" r:id="rId5"/>
     <sheet name="Supervisor_QA" sheetId="9" r:id="rId6"/>
